--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>34.60835929945203</v>
+      </c>
+      <c r="C2">
         <v>25.67086601482755</v>
-      </c>
-      <c r="C2">
-        <v>34.60835929945203</v>
       </c>
       <c r="D2">
         <v>3.895466555052711</v>
       </c>
       <c r="E2">
+        <v>21.59254215984079</v>
+      </c>
+      <c r="F2">
+        <v>62.39111762857443</v>
+      </c>
+      <c r="G2">
         <v>16.01634021158479</v>
-      </c>
-      <c r="F2">
-        <v>62.39111762857442</v>
-      </c>
-      <c r="G2">
-        <v>21.59254215984079</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>43.83561643835616</v>
+      </c>
+      <c r="C3">
         <v>57.80821917808219</v>
-      </c>
-      <c r="C3">
-        <v>43.83561643835616</v>
       </c>
       <c r="D3">
         <v>1.729857819905213</v>
       </c>
       <c r="E3">
-        <v>28.66847826086956</v>
+        <v>21.73913043478261</v>
       </c>
       <c r="F3">
         <v>49.59239130434782</v>
       </c>
       <c r="G3">
-        <v>21.73913043478261</v>
+        <v>28.66847826086956</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>37.71428571428572</v>
+      </c>
+      <c r="C4">
         <v>39.14285714285714</v>
-      </c>
-      <c r="C4">
-        <v>37.71428571428572</v>
       </c>
       <c r="D4">
         <v>2.554744525547445</v>
       </c>
       <c r="E4">
-        <v>22.1324717285945</v>
+        <v>21.32471728594507</v>
       </c>
       <c r="F4">
         <v>56.54281098546042</v>
       </c>
       <c r="G4">
-        <v>21.32471728594507</v>
+        <v>22.1324717285945</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>42.01680672268908</v>
+      </c>
+      <c r="C5">
         <v>34.87394957983193</v>
-      </c>
-      <c r="C5">
-        <v>42.01680672268908</v>
       </c>
       <c r="D5">
         <v>2.867469879518072</v>
       </c>
       <c r="E5">
-        <v>19.71496437054632</v>
+        <v>23.75296912114015</v>
       </c>
       <c r="F5">
         <v>56.53206650831354</v>
       </c>
       <c r="G5">
-        <v>23.75296912114015</v>
+        <v>19.71496437054632</v>
       </c>
     </row>
   </sheetData>
